--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_calcium/harmonized.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_calcium/harmonized.xlsx
@@ -432,7 +432,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="47" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -614,12 +614,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3:3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -662,12 +662,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4:4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -710,12 +710,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5:5</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1:6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -806,12 +806,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2:7</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3:8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -902,12 +902,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4:9</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -950,12 +950,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5:10</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -998,12 +998,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6:11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8:12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -4414,12 +4414,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>4:20-29</t>
+          <t>Hu:4:20-29</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>4:10-20</t>
+          <t>Hu:4:10-20</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4518,12 +4518,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>4:0-10</t>
+          <t>Hu:4:0-10</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4553,7 +4553,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4570,12 +4570,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>4:-10-0</t>
+          <t>Ho:4:-10-0</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4605,7 +4605,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4622,12 +4622,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>4:-20--10</t>
+          <t>Ho:4:-20--10</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>4:-30--20</t>
+          <t>Ho:4:-30--20</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4709,7 +4709,7 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4778,12 +4778,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4813,7 +4813,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4830,12 +4830,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4882,12 +4882,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4934,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>4:-80--70</t>
+          <t>Ho:4:-80--70</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4969,7 +4969,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5021,7 +5021,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>4:-100--90</t>
+          <t>Ho:4:-100--90</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5073,7 +5073,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5090,12 +5090,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5142,12 +5142,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>4:-150--125</t>
+          <t>Ho:4:-150--125</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5246,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>4:-200--175</t>
+          <t>Ho:4:-200--175</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5350,12 +5350,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>5:0-24</t>
+          <t>Hu:5:0-24</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5402,12 +5402,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>5:10-18</t>
+          <t>Hu:5:10-18</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5454,12 +5454,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>5:0-10</t>
+          <t>Hu:5:0-10</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5489,7 +5489,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>5:-10-0</t>
+          <t>Ho:5:-10-0</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5541,7 +5541,7 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5558,12 +5558,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Ho:5:-20--10</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5610,12 +5610,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Ho:5:-30--20</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5645,7 +5645,7 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5662,12 +5662,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5766,12 +5766,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>5:-80--70</t>
+          <t>Ho:5:-80--70</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5922,12 +5922,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5957,7 +5957,7 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>5:-100--90</t>
+          <t>Ho:5:-100--90</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6009,7 +6009,7 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6026,12 +6026,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6061,7 +6061,7 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>5:-150--125</t>
+          <t>Ho:5:-150--125</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>5:-200--175</t>
+          <t>Ho:5:-200--175</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6217,7 +6217,7 @@
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6234,12 +6234,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6269,7 +6269,7 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6286,12 +6286,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>5:-300--250</t>
+          <t>Ho:5:-300--250</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6321,7 +6321,7 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>6:20-30</t>
+          <t>Hu:6:20-30</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6390,12 +6390,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6425,7 +6425,7 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6442,12 +6442,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6546,12 +6546,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6581,7 +6581,7 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6598,12 +6598,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>6:-10-0</t>
+          <t>Ho:6:-10-0</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6633,7 +6633,7 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>6:-20--10</t>
+          <t>Ho:6:-20--10</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>6:-30--20</t>
+          <t>Ho:6:-30--20</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6789,7 +6789,7 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6858,12 +6858,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6910,12 +6910,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6945,7 +6945,7 @@
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6962,12 +6962,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>6:-80--70</t>
+          <t>Ho:6:-80--70</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7014,12 +7014,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7049,7 +7049,7 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7066,12 +7066,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>6:-100--90</t>
+          <t>Ho:6:-100--90</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7101,7 +7101,7 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7118,12 +7118,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7170,12 +7170,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>6:-150--125</t>
+          <t>Ho:6:-150--125</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7205,7 +7205,7 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>6:-200--175</t>
+          <t>Ho:6:-200--175</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7326,12 +7326,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7430,12 +7430,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>7:20-22</t>
+          <t>Hu:7:20-22</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7482,12 +7482,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>7:10-20</t>
+          <t>Hu:7:10-20</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7534,12 +7534,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7569,7 +7569,7 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7586,12 +7586,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>7:-10-0</t>
+          <t>Ho:7:-10-0</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7638,12 +7638,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>7:-20--10</t>
+          <t>Ho:7:-20--10</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7673,7 +7673,7 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7690,12 +7690,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>7:-30--20</t>
+          <t>Ho:7:-30--20</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7742,12 +7742,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>7:-40--30</t>
+          <t>Ho:7:-40--30</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7846,12 +7846,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -7933,7 +7933,7 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7950,12 +7950,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>7:-80--70</t>
+          <t>Ho:7:-80--70</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -7985,7 +7985,7 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8002,12 +8002,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>7:-100--90</t>
+          <t>Ho:7:-100--90</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8106,12 +8106,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8141,7 +8141,7 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8158,12 +8158,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>7:-150--125</t>
+          <t>Ho:7:-150--125</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8210,12 +8210,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8245,7 +8245,7 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8262,12 +8262,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>7:-200--175</t>
+          <t>Ho:7:-200--175</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8314,12 +8314,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8349,7 +8349,7 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8366,12 +8366,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>7:-300--250</t>
+          <t>Ho:7:-300--250</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8401,7 +8401,7 @@
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>8:10-20</t>
+          <t>Hu:8:10-20</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -8453,7 +8453,7 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>8:0-10</t>
+          <t>Hu:8:0-10</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8522,12 +8522,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Hu:8:-10-0</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8574,12 +8574,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Ho:8:-10-0</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8609,7 +8609,7 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8626,12 +8626,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>8:-20--10</t>
+          <t>Ho:8:-20--10</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8678,12 +8678,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>8:-30--20</t>
+          <t>Ho:8:-30--20</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8730,12 +8730,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8782,12 +8782,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -8817,7 +8817,7 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -8869,7 +8869,7 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8886,12 +8886,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -8921,7 +8921,7 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8938,12 +8938,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>8:-80--70</t>
+          <t>Ho:8:-80--70</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8990,12 +8990,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9025,7 +9025,7 @@
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9042,12 +9042,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>8:-100--90</t>
+          <t>Ho:8:-100--90</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9146,12 +9146,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>8:-150--125</t>
+          <t>Ho:8:-150--125</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9198,12 +9198,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9250,12 +9250,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9285,7 +9285,7 @@
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9302,12 +9302,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>9:10-18</t>
+          <t>Hu:9:10-18</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9337,7 +9337,7 @@
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9354,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>9:0-10</t>
+          <t>Hu:9:0-10</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9389,7 +9389,7 @@
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9406,12 +9406,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>9:-10-0</t>
+          <t>Ho:9:-10-0</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9441,7 +9441,7 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9458,12 +9458,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>9:-20--10</t>
+          <t>Ho:9:-20--10</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9510,12 +9510,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>9:-30--20</t>
+          <t>Ho:9:-30--20</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9562,12 +9562,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>9:-40--30</t>
+          <t>Ho:9:-40--30</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -9597,7 +9597,7 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9614,12 +9614,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9649,7 +9649,7 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9666,12 +9666,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9718,12 +9718,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9753,7 +9753,7 @@
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9770,12 +9770,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>9:-80--70</t>
+          <t>Ho:9:-80--70</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9822,12 +9822,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -9857,7 +9857,7 @@
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9874,12 +9874,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>9:-100--90</t>
+          <t>Ho:9:-100--90</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9926,12 +9926,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>9:-150--125</t>
+          <t>Ho:9:-150--125</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10013,7 +10013,7 @@
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10030,12 +10030,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10082,12 +10082,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>9:-200--175</t>
+          <t>Ho:9:-200--175</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10134,12 +10134,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10169,7 +10169,7 @@
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10186,12 +10186,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>9:-300--250</t>
+          <t>Ho:9:-300--250</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10221,7 +10221,7 @@
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10238,12 +10238,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>10:20-29</t>
+          <t>Hu:10:20-29</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10273,7 +10273,7 @@
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10290,12 +10290,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>10:10-20</t>
+          <t>Hu:10:10-20</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10342,12 +10342,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>10:0-10</t>
+          <t>Hu:10:0-10</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10394,12 +10394,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>10:-10-0</t>
+          <t>Ho:10:-10-0</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10429,7 +10429,7 @@
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10446,12 +10446,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>10:-20--10</t>
+          <t>Ho:10:-20--10</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10498,12 +10498,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>10:-30--20</t>
+          <t>Ho:10:-30--20</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10533,7 +10533,7 @@
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10585,7 +10585,7 @@
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10602,12 +10602,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10637,7 +10637,7 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10654,12 +10654,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -10689,7 +10689,7 @@
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10706,12 +10706,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -10741,7 +10741,7 @@
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10758,12 +10758,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>10:-80--70</t>
+          <t>Ho:10:-80--70</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -10793,7 +10793,7 @@
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -10845,7 +10845,7 @@
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10862,12 +10862,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>10:-100--90</t>
+          <t>Ho:10:-100--90</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -10897,7 +10897,7 @@
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10914,12 +10914,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10966,12 +10966,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>10:-150--125</t>
+          <t>Ho:10:-150--125</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -11001,7 +11001,7 @@
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11018,12 +11018,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11053,7 +11053,7 @@
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11070,12 +11070,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>10:-200--175</t>
+          <t>Ho:10:-200--175</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11105,7 +11105,7 @@
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11122,12 +11122,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11157,7 +11157,7 @@
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11174,12 +11174,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -11209,7 +11209,7 @@
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11226,12 +11226,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -11261,7 +11261,7 @@
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11278,12 +11278,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>11:10-18</t>
+          <t>Hu:11:10-18</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -11313,7 +11313,7 @@
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11330,12 +11330,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>11:0-10</t>
+          <t>Hu:11:0-10</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -11365,7 +11365,7 @@
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11382,12 +11382,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>11:-10-0</t>
+          <t>Ho:11:-10-0</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -11417,7 +11417,7 @@
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11434,12 +11434,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>11:-20--10</t>
+          <t>Ho:11:-20--10</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -11469,7 +11469,7 @@
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11486,12 +11486,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>11:-30--20</t>
+          <t>Ho:11:-30--20</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11538,12 +11538,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>11:-40--30</t>
+          <t>Ho:11:-40--30</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -11573,7 +11573,7 @@
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11590,12 +11590,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -11625,7 +11625,7 @@
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11642,12 +11642,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -11677,7 +11677,7 @@
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11694,12 +11694,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -11729,7 +11729,7 @@
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11746,12 +11746,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>11:-80--70</t>
+          <t>Ho:11:-80--70</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11798,12 +11798,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -11833,7 +11833,7 @@
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>11:-100--90</t>
+          <t>Ho:11:-100--90</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -11885,7 +11885,7 @@
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11902,12 +11902,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11954,12 +11954,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>11:-150--125</t>
+          <t>Ho:11:-150--125</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12006,12 +12006,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12041,7 +12041,7 @@
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12058,12 +12058,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>11:-200--175</t>
+          <t>Ho:11:-200--175</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -12093,7 +12093,7 @@
       <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12110,12 +12110,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12145,7 +12145,7 @@
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12162,12 +12162,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>13:20-25</t>
+          <t>Hu:13:20-25</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -12197,7 +12197,7 @@
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12214,12 +12214,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>13:10-20</t>
+          <t>Hu:13:10-20</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -12249,7 +12249,7 @@
       <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12266,12 +12266,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>13:0-10</t>
+          <t>Hu:13:0-10</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -12301,7 +12301,7 @@
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12318,12 +12318,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Hu:13:-10-0</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12353,7 +12353,7 @@
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12370,12 +12370,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Ho:13:-10-0</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -12405,7 +12405,7 @@
       <c r="K235" s="2" t="inlineStr"/>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12422,12 +12422,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>13:-20--10</t>
+          <t>Ho:13:-20--10</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12474,12 +12474,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>13:-30--20</t>
+          <t>Ho:13:-30--20</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -12509,7 +12509,7 @@
       <c r="K237" s="2" t="inlineStr"/>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12526,12 +12526,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12561,7 +12561,7 @@
       <c r="K238" s="2" t="inlineStr"/>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12578,12 +12578,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12630,12 +12630,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -12665,7 +12665,7 @@
       <c r="K240" s="2" t="inlineStr"/>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12682,12 +12682,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -12717,7 +12717,7 @@
       <c r="K241" s="2" t="inlineStr"/>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12734,12 +12734,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>13:-80--70</t>
+          <t>Ho:13:-80--70</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -12769,7 +12769,7 @@
       <c r="K242" s="2" t="inlineStr"/>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12786,12 +12786,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -12821,7 +12821,7 @@
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12838,12 +12838,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>13:-100--90</t>
+          <t>Ho:13:-100--90</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -12873,7 +12873,7 @@
       <c r="K244" s="2" t="inlineStr"/>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -12925,7 +12925,7 @@
       <c r="K245" s="2" t="inlineStr"/>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12942,12 +12942,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>13:-150--125</t>
+          <t>Ho:13:-150--125</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -12977,7 +12977,7 @@
       <c r="K246" s="2" t="inlineStr"/>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12994,12 +12994,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -13029,7 +13029,7 @@
       <c r="K247" s="2" t="inlineStr"/>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13046,12 +13046,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>13:-200--175</t>
+          <t>Ho:13:-200--175</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -13081,7 +13081,7 @@
       <c r="K248" s="2" t="inlineStr"/>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13098,12 +13098,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -13133,7 +13133,7 @@
       <c r="K249" s="2" t="inlineStr"/>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13150,12 +13150,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -13185,7 +13185,7 @@
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13202,12 +13202,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -13237,7 +13237,7 @@
       <c r="K251" s="2" t="inlineStr"/>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13254,12 +13254,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>14:0-10</t>
+          <t>Hu:14:0-10</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       <c r="K252" s="2" t="inlineStr"/>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13306,12 +13306,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>14:-10-0</t>
+          <t>Ho:14:-10-0</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -13341,7 +13341,7 @@
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13358,12 +13358,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>14:-20--10</t>
+          <t>Ho:14:-20--10</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -13393,7 +13393,7 @@
       <c r="K254" s="2" t="inlineStr"/>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13410,12 +13410,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>14:-30--20</t>
+          <t>Ho:14:-30--20</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -13445,7 +13445,7 @@
       <c r="K255" s="2" t="inlineStr"/>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13462,12 +13462,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>14:-40--30</t>
+          <t>Ho:14:-40--30</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -13497,7 +13497,7 @@
       <c r="K256" s="2" t="inlineStr"/>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13514,12 +13514,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>14:-50--40</t>
+          <t>Ho:14:-50--40</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -13549,7 +13549,7 @@
       <c r="K257" s="2" t="inlineStr"/>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13566,12 +13566,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -13601,7 +13601,7 @@
       <c r="K258" s="2" t="inlineStr"/>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13618,12 +13618,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -13653,7 +13653,7 @@
       <c r="K259" s="2" t="inlineStr"/>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13670,12 +13670,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>14:-80--70</t>
+          <t>Ho:14:-80--70</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -13705,7 +13705,7 @@
       <c r="K260" s="2" t="inlineStr"/>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13722,12 +13722,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -13757,7 +13757,7 @@
       <c r="K261" s="2" t="inlineStr"/>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13774,12 +13774,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>14:-100--90</t>
+          <t>Ho:14:-100--90</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -13809,7 +13809,7 @@
       <c r="K262" s="2" t="inlineStr"/>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13826,12 +13826,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -13861,7 +13861,7 @@
       <c r="K263" s="2" t="inlineStr"/>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13878,12 +13878,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>14:-150--125</t>
+          <t>Ho:14:-150--125</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -13913,7 +13913,7 @@
       <c r="K264" s="2" t="inlineStr"/>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13930,12 +13930,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -13965,7 +13965,7 @@
       <c r="K265" s="2" t="inlineStr"/>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13982,12 +13982,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>14:-200--175</t>
+          <t>Ho:14:-200--175</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -14017,7 +14017,7 @@
       <c r="K266" s="2" t="inlineStr"/>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14034,12 +14034,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -14069,7 +14069,7 @@
       <c r="K267" s="2" t="inlineStr"/>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14086,12 +14086,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>14:-220--215</t>
+          <t>Ho:14:-220--215</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -14121,7 +14121,7 @@
       <c r="K268" s="2" t="inlineStr"/>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14138,12 +14138,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>15:20-24</t>
+          <t>Hu:15:20-24</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -14173,7 +14173,7 @@
       <c r="K269" s="2" t="inlineStr"/>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14190,12 +14190,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>15:10-20</t>
+          <t>Hu:15:10-20</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -14225,7 +14225,7 @@
       <c r="K270" s="2" t="inlineStr"/>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14242,12 +14242,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>15:0-10</t>
+          <t>Hu:15:0-10</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -14277,7 +14277,7 @@
       <c r="K271" s="2" t="inlineStr"/>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14294,12 +14294,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Hu:15:-10-0</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -14329,7 +14329,7 @@
       <c r="K272" s="2" t="inlineStr"/>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14346,12 +14346,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Ho:15:-10-0</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -14381,7 +14381,7 @@
       <c r="K273" s="2" t="inlineStr"/>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14398,12 +14398,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>15:-20--10</t>
+          <t>Ho:15:-20--10</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -14433,7 +14433,7 @@
       <c r="K274" s="2" t="inlineStr"/>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14450,12 +14450,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>15:-30--20</t>
+          <t>Ho:15:-30--20</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -14485,7 +14485,7 @@
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14502,12 +14502,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -14537,7 +14537,7 @@
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14554,12 +14554,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -14589,7 +14589,7 @@
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -14641,7 +14641,7 @@
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14658,12 +14658,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -14693,7 +14693,7 @@
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14710,12 +14710,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>15:-80--70</t>
+          <t>Ho:15:-80--70</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -14745,7 +14745,7 @@
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14762,12 +14762,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -14797,7 +14797,7 @@
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14814,12 +14814,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>15:-100--90</t>
+          <t>Ho:15:-100--90</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -14849,7 +14849,7 @@
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14866,12 +14866,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -14901,7 +14901,7 @@
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14918,12 +14918,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>15:-150--125</t>
+          <t>Ho:15:-150--125</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -14953,7 +14953,7 @@
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14970,12 +14970,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>16:20-29</t>
+          <t>Hu:16:20-29</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -15005,7 +15005,7 @@
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15022,12 +15022,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>16:10-20</t>
+          <t>Hu:16:10-20</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -15057,7 +15057,7 @@
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15074,12 +15074,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>16:0-10</t>
+          <t>Hu:16:0-10</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -15109,7 +15109,7 @@
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15126,12 +15126,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Hu:16:-10-0</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -15161,7 +15161,7 @@
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15178,12 +15178,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Ho:16:-10-0</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -15213,7 +15213,7 @@
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15230,12 +15230,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>16:-20--10</t>
+          <t>Ho:16:-20--10</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -15265,7 +15265,7 @@
       <c r="K290" s="2" t="inlineStr"/>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15282,12 +15282,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>16:-30--20</t>
+          <t>Ho:16:-30--20</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -15317,7 +15317,7 @@
       <c r="K291" s="2" t="inlineStr"/>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15334,12 +15334,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -15369,7 +15369,7 @@
       <c r="K292" s="2" t="inlineStr"/>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15386,12 +15386,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -15421,7 +15421,7 @@
       <c r="K293" s="2" t="inlineStr"/>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15438,12 +15438,12 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -15473,7 +15473,7 @@
       <c r="K294" s="2" t="inlineStr"/>
       <c r="L294" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15490,12 +15490,12 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -15525,7 +15525,7 @@
       <c r="K295" s="2" t="inlineStr"/>
       <c r="L295" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15542,12 +15542,12 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>16:-80--70</t>
+          <t>Ho:16:-80--70</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -15577,7 +15577,7 @@
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15594,12 +15594,12 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -15629,7 +15629,7 @@
       <c r="K297" s="2" t="inlineStr"/>
       <c r="L297" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15646,12 +15646,12 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>16:-100--90</t>
+          <t>Ho:16:-100--90</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -15681,7 +15681,7 @@
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15698,12 +15698,12 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -15733,7 +15733,7 @@
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15750,12 +15750,12 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>16:-150--125</t>
+          <t>Ho:16:-150--125</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -15785,7 +15785,7 @@
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15802,12 +15802,12 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -15837,7 +15837,7 @@
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15854,12 +15854,12 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>16:-200--175</t>
+          <t>Ho:16:-200--175</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -15889,7 +15889,7 @@
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15906,12 +15906,12 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -15941,7 +15941,7 @@
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15958,12 +15958,12 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>17:20-25</t>
+          <t>Hu:17:20-25</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -15993,7 +15993,7 @@
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16010,12 +16010,12 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>17:10-20</t>
+          <t>Hu:17:10-20</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -16045,7 +16045,7 @@
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16062,12 +16062,12 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>17:0-10</t>
+          <t>Hu:17:0-10</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -16097,7 +16097,7 @@
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16114,12 +16114,12 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Hu:17:-10-0</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -16149,7 +16149,7 @@
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16166,12 +16166,12 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Ho:17:-10-0</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       <c r="K308" s="2" t="inlineStr"/>
       <c r="L308" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16218,12 +16218,12 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>17:-20--10</t>
+          <t>Ho:17:-20--10</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -16253,7 +16253,7 @@
       <c r="K309" s="2" t="inlineStr"/>
       <c r="L309" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16270,12 +16270,12 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -16305,7 +16305,7 @@
       <c r="K310" s="2" t="inlineStr"/>
       <c r="L310" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16322,12 +16322,12 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -16357,7 +16357,7 @@
       <c r="K311" s="2" t="inlineStr"/>
       <c r="L311" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16374,12 +16374,12 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -16409,7 +16409,7 @@
       <c r="K312" s="2" t="inlineStr"/>
       <c r="L312" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16426,12 +16426,12 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -16461,7 +16461,7 @@
       <c r="K313" s="2" t="inlineStr"/>
       <c r="L313" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16478,12 +16478,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -16513,7 +16513,7 @@
       <c r="K314" s="2" t="inlineStr"/>
       <c r="L314" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16530,12 +16530,12 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>17:-80--70</t>
+          <t>Ho:17:-80--70</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -16565,7 +16565,7 @@
       <c r="K315" s="2" t="inlineStr"/>
       <c r="L315" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16582,12 +16582,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -16617,7 +16617,7 @@
       <c r="K316" s="2" t="inlineStr"/>
       <c r="L316" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16634,12 +16634,12 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>17:-100--90</t>
+          <t>Ho:17:-100--90</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -16669,7 +16669,7 @@
       <c r="K317" s="2" t="inlineStr"/>
       <c r="L317" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16686,12 +16686,12 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -16721,7 +16721,7 @@
       <c r="K318" s="2" t="inlineStr"/>
       <c r="L318" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16738,12 +16738,12 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>17:-150--125</t>
+          <t>Ho:17:-150--125</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -16773,7 +16773,7 @@
       <c r="K319" s="2" t="inlineStr"/>
       <c r="L319" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16790,12 +16790,12 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -16825,7 +16825,7 @@
       <c r="K320" s="2" t="inlineStr"/>
       <c r="L320" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16842,12 +16842,12 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>17:-200--175</t>
+          <t>Ho:17:-200--175</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -16877,7 +16877,7 @@
       <c r="K321" s="2" t="inlineStr"/>
       <c r="L321" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16894,12 +16894,12 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -16929,7 +16929,7 @@
       <c r="K322" s="2" t="inlineStr"/>
       <c r="L322" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16946,12 +16946,12 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>19:10-20</t>
+          <t>Hu:19:10-20</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -16981,7 +16981,7 @@
       <c r="K323" s="2" t="inlineStr"/>
       <c r="L323" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16998,12 +16998,12 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>19:0-10</t>
+          <t>Hu:19:0-10</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -17033,7 +17033,7 @@
       <c r="K324" s="2" t="inlineStr"/>
       <c r="L324" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17050,12 +17050,12 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>19:-10-0</t>
+          <t>Ho:19:-10-0</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -17085,7 +17085,7 @@
       <c r="K325" s="2" t="inlineStr"/>
       <c r="L325" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17102,12 +17102,12 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>19:-20--10</t>
+          <t>Ho:19:-20--10</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -17137,7 +17137,7 @@
       <c r="K326" s="2" t="inlineStr"/>
       <c r="L326" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17154,12 +17154,12 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>19:-30--20</t>
+          <t>Ho:19:-30--20</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -17189,7 +17189,7 @@
       <c r="K327" s="2" t="inlineStr"/>
       <c r="L327" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17206,12 +17206,12 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -17241,7 +17241,7 @@
       <c r="K328" s="2" t="inlineStr"/>
       <c r="L328" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17258,12 +17258,12 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -17293,7 +17293,7 @@
       <c r="K329" s="2" t="inlineStr"/>
       <c r="L329" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17310,12 +17310,12 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -17345,7 +17345,7 @@
       <c r="K330" s="2" t="inlineStr"/>
       <c r="L330" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17362,12 +17362,12 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -17397,7 +17397,7 @@
       <c r="K331" s="2" t="inlineStr"/>
       <c r="L331" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17414,12 +17414,12 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>19:-80--70</t>
+          <t>Ho:19:-80--70</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -17449,7 +17449,7 @@
       <c r="K332" s="2" t="inlineStr"/>
       <c r="L332" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17466,12 +17466,12 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -17501,7 +17501,7 @@
       <c r="K333" s="2" t="inlineStr"/>
       <c r="L333" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17518,12 +17518,12 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>19:-100--90</t>
+          <t>Ho:19:-100--90</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -17553,7 +17553,7 @@
       <c r="K334" s="2" t="inlineStr"/>
       <c r="L334" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17570,12 +17570,12 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -17605,7 +17605,7 @@
       <c r="K335" s="2" t="inlineStr"/>
       <c r="L335" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17622,12 +17622,12 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>19:-150--125</t>
+          <t>Ho:19:-150--125</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -17657,7 +17657,7 @@
       <c r="K336" s="2" t="inlineStr"/>
       <c r="L336" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17674,12 +17674,12 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -17709,7 +17709,7 @@
       <c r="K337" s="2" t="inlineStr"/>
       <c r="L337" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17726,12 +17726,12 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>19:-200--175</t>
+          <t>Ho:19:-200--175</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -17761,7 +17761,7 @@
       <c r="K338" s="2" t="inlineStr"/>
       <c r="L338" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17778,12 +17778,12 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -17813,7 +17813,7 @@
       <c r="K339" s="2" t="inlineStr"/>
       <c r="L339" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17830,12 +17830,12 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>19:-250--216</t>
+          <t>Ho:19:-250--216</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -17865,7 +17865,7 @@
       <c r="K340" s="2" t="inlineStr"/>
       <c r="L340" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17882,12 +17882,12 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>20:10-19</t>
+          <t>Hu:20:10-19</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -17917,7 +17917,7 @@
       <c r="K341" s="2" t="inlineStr"/>
       <c r="L341" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17934,12 +17934,12 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>20:0-10</t>
+          <t>Hu:20:0-10</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -17969,7 +17969,7 @@
       <c r="K342" s="2" t="inlineStr"/>
       <c r="L342" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17986,12 +17986,12 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Hu:20:-10-0</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -18021,7 +18021,7 @@
       <c r="K343" s="2" t="inlineStr"/>
       <c r="L343" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18038,12 +18038,12 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Ho:20:-10-0</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -18073,7 +18073,7 @@
       <c r="K344" s="2" t="inlineStr"/>
       <c r="L344" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18090,12 +18090,12 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>20:-20--10</t>
+          <t>Ho:20:-20--10</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -18125,7 +18125,7 @@
       <c r="K345" s="2" t="inlineStr"/>
       <c r="L345" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18142,12 +18142,12 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>20:-30--20</t>
+          <t>Ho:20:-30--20</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -18177,7 +18177,7 @@
       <c r="K346" s="2" t="inlineStr"/>
       <c r="L346" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18194,12 +18194,12 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -18229,7 +18229,7 @@
       <c r="K347" s="2" t="inlineStr"/>
       <c r="L347" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18246,12 +18246,12 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -18281,7 +18281,7 @@
       <c r="K348" s="2" t="inlineStr"/>
       <c r="L348" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18298,12 +18298,12 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -18333,7 +18333,7 @@
       <c r="K349" s="2" t="inlineStr"/>
       <c r="L349" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18350,12 +18350,12 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -18385,7 +18385,7 @@
       <c r="K350" s="2" t="inlineStr"/>
       <c r="L350" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18402,12 +18402,12 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>20:-80--70</t>
+          <t>Ho:20:-80--70</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -18437,7 +18437,7 @@
       <c r="K351" s="2" t="inlineStr"/>
       <c r="L351" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18454,12 +18454,12 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -18489,7 +18489,7 @@
       <c r="K352" s="2" t="inlineStr"/>
       <c r="L352" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18506,12 +18506,12 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>20:-100--90</t>
+          <t>Ho:20:-100--90</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -18541,7 +18541,7 @@
       <c r="K353" s="2" t="inlineStr"/>
       <c r="L353" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18558,12 +18558,12 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -18593,7 +18593,7 @@
       <c r="K354" s="2" t="inlineStr"/>
       <c r="L354" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18610,12 +18610,12 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>20:-150--125</t>
+          <t>Ho:20:-150--125</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -18645,7 +18645,7 @@
       <c r="K355" s="2" t="inlineStr"/>
       <c r="L355" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18662,12 +18662,12 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -18697,7 +18697,7 @@
       <c r="K356" s="2" t="inlineStr"/>
       <c r="L356" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18714,12 +18714,12 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>20:-200--175</t>
+          <t>Ho:20:-200--175</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -18749,7 +18749,7 @@
       <c r="K357" s="2" t="inlineStr"/>
       <c r="L357" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18766,12 +18766,12 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -18801,7 +18801,7 @@
       <c r="K358" s="2" t="inlineStr"/>
       <c r="L358" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18818,12 +18818,12 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>20:-300--250</t>
+          <t>Ho:20:-300--250</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -18853,7 +18853,7 @@
       <c r="K359" s="2" t="inlineStr"/>
       <c r="L359" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18870,12 +18870,12 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>21:10-20</t>
+          <t>Hu:21:10-20</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -18905,7 +18905,7 @@
       <c r="K360" s="2" t="inlineStr"/>
       <c r="L360" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18922,12 +18922,12 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>21:0-10</t>
+          <t>Hu:21:0-10</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -18957,7 +18957,7 @@
       <c r="K361" s="2" t="inlineStr"/>
       <c r="L361" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18974,12 +18974,12 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>21:-10-0</t>
+          <t>Ho:21:-10-0</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -19009,7 +19009,7 @@
       <c r="K362" s="2" t="inlineStr"/>
       <c r="L362" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19026,12 +19026,12 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>21:-20--10</t>
+          <t>Ho:21:-20--10</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -19061,7 +19061,7 @@
       <c r="K363" s="2" t="inlineStr"/>
       <c r="L363" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19078,12 +19078,12 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>21:-30--20</t>
+          <t>Ho:21:-30--20</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -19113,7 +19113,7 @@
       <c r="K364" s="2" t="inlineStr"/>
       <c r="L364" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19130,12 +19130,12 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>21:-40--30</t>
+          <t>Ho:21:-40--30</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -19165,7 +19165,7 @@
       <c r="K365" s="2" t="inlineStr"/>
       <c r="L365" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19182,12 +19182,12 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -19217,7 +19217,7 @@
       <c r="K366" s="2" t="inlineStr"/>
       <c r="L366" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19234,12 +19234,12 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>21:-60--50</t>
+          <t>Ho:21:-60--50</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -19269,7 +19269,7 @@
       <c r="K367" s="2" t="inlineStr"/>
       <c r="L367" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19286,12 +19286,12 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -19321,7 +19321,7 @@
       <c r="K368" s="2" t="inlineStr"/>
       <c r="L368" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19338,12 +19338,12 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>21:-80--70</t>
+          <t>Ho:21:-80--70</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
@@ -19373,7 +19373,7 @@
       <c r="K369" s="2" t="inlineStr"/>
       <c r="L369" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19390,12 +19390,12 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -19425,7 +19425,7 @@
       <c r="K370" s="2" t="inlineStr"/>
       <c r="L370" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19442,12 +19442,12 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>21:-100--90</t>
+          <t>Ho:21:-100--90</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
@@ -19477,7 +19477,7 @@
       <c r="K371" s="2" t="inlineStr"/>
       <c r="L371" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19494,12 +19494,12 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -19529,7 +19529,7 @@
       <c r="K372" s="2" t="inlineStr"/>
       <c r="L372" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19546,12 +19546,12 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>21:-150--125</t>
+          <t>Ho:21:-150--125</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -19581,7 +19581,7 @@
       <c r="K373" s="2" t="inlineStr"/>
       <c r="L373" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19598,12 +19598,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -19633,7 +19633,7 @@
       <c r="K374" s="2" t="inlineStr"/>
       <c r="L374" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19650,12 +19650,12 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>21:-200--175</t>
+          <t>Ho:21:-200--175</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -19685,7 +19685,7 @@
       <c r="K375" s="2" t="inlineStr"/>
       <c r="L375" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19702,12 +19702,12 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-250--200</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -19737,7 +19737,7 @@
       <c r="K376" s="2" t="inlineStr"/>
       <c r="L376" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
